--- a/Copy of AI_AuditLog_Example.xlsx
+++ b/Copy of AI_AuditLog_Example.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\swr\auditlog\ai-audit-log-hyycichu-cell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7434B7C4-5E0A-48F1-AB42-C98005950FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B194E3-6FF6-49C9-9782-EE8797C37459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="107">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>Healthcare Booking System</t>
+  </si>
+  <si>
+    <t>iiiii</t>
   </si>
 </sst>
 </file>
@@ -545,23 +548,23 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,14 +878,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -917,7 +920,7 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1067,24 +1070,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1354,28 +1357,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1629,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1638,28 +1641,28 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>72</v>
       </c>
@@ -1673,7 +1676,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>76</v>
       </c>
@@ -1685,7 +1688,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>79</v>
       </c>
@@ -1697,7 +1700,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>81</v>
       </c>
@@ -1708,8 +1711,11 @@
         <v>78</v>
       </c>
       <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>83</v>
       </c>
@@ -1721,7 +1727,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>85</v>
       </c>
@@ -1733,12 +1739,12 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>72</v>
       </c>
@@ -1752,7 +1758,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>76</v>
       </c>
@@ -1764,7 +1770,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>79</v>
       </c>
@@ -1776,7 +1782,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>81</v>
       </c>
